--- a/LubanConfig/Moba/Production/Datas/T-特效表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/T-特效表.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -828,6 +828,202 @@
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n">
+        <v>90007001</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_skill1_roll</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n">
+        <v>90007002</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_skill2_grenade</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n">
+        <v>90007003</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_skill2_explosion</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n">
+        <v>90007004</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_skill3_cannon</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n">
+        <v>90007005</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_buff_enhanced</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n">
+        <v>90007006</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>effect/sunshangxiang_buff_mark</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n">
+        <v>90008001</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_basic_bullet</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n">
+        <v>90008002</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_skill1_grenade</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n">
+        <v>90008003</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_skill1_explosion</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n">
+        <v>90008004</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_skill2_cannon</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n">
+        <v>90008005</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_passive_sweep</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n">
+        <v>90008006</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>effect/luban_skill3_bomb</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n">
+        <v>90001002</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>effect/lianpo_skill1_charge</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n">
+        <v>90001003</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>effect/lianpo_skill3_impact</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -841,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1704,6 +1900,812 @@
       <c r="U11" s="2" t="n"/>
       <c r="V11" s="2" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>90007001</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>90007001</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="J12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007001</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>90007002</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>90007002</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007002</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>90007003</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>90007003</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007003</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>90007004</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>90007004</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007004</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>90007005</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>90007005</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007005</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>90007006</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>90007006</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90007006</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>90008001</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>90008001</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008001</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>90008002</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>90008002</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008002</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n">
+        <v>90008003</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>90008003</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="J20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008003</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>90008004</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>90008004</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="J21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008004</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>90008005</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>90008005</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="J22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008005</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>90008006</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>90008006</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="J23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_90008006</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>90001002</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>90001002</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="J24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>lianpo_charge_placeholder</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
